--- a/tame_output/ON/bt/strategyON_20230729.xlsx
+++ b/tame_output/ON/bt/strategyON_20230729.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.8%</t>
+          <t>456.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,16 +1217,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>141.8%</t>
+          <t>141.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>136.2%</t>
+          <t>136.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1672"/>
+  <dimension ref="A1:G1673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39966,7 +39966,7 @@
         <v>45134</v>
       </c>
       <c r="B1672" t="n">
-        <v>2.879364175590628</v>
+        <v>2.879619907626983</v>
       </c>
       <c r="C1672" t="n">
         <v>3.013863868964772</v>
@@ -39982,6 +39982,29 @@
       </c>
       <c r="G1672" t="n">
         <v>4.290410578202381</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="2" t="n">
+        <v>45135</v>
+      </c>
+      <c r="B1673" t="n">
+        <v>2.883953355817033</v>
+      </c>
+      <c r="C1673" t="n">
+        <v>3.015113123698972</v>
+      </c>
+      <c r="D1673" t="n">
+        <v>1.522731884967649</v>
+      </c>
+      <c r="E1673" t="n">
+        <v>3.623849453372285</v>
+      </c>
+      <c r="F1673" t="n">
+        <v>2.127916880692788</v>
+      </c>
+      <c r="G1673" t="n">
+        <v>4.291863252114647</v>
       </c>
     </row>
   </sheetData>
